--- a/results/greedy/UAVs9_GRID13/tour/UAVs9_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs9_GRID13/tour/UAVs9_GRID13_1920_16_Greedy_sequences.xlsx
@@ -622,7 +622,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02286970795830712</v>
+        <v>0.02312658401206136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02801975002512336</v>
+        <v>0.02687579102348536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02044195798225701</v>
+        <v>0.02058833400951698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02764275000663474</v>
+        <v>0.02711787499720231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02776158298365772</v>
+        <v>0.0281692499993369</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02621824998641387</v>
+        <v>0.02603091701166704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276716602500528</v>
+        <v>0.02247491700109094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02088033297332004</v>
+        <v>0.02017541701206937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02321491698967293</v>
+        <v>0.02267987502273172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02272841596277431</v>
+        <v>0.02311916596954688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02061204198980704</v>
+        <v>0.02023733296664432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02424191602040082</v>
+        <v>0.02386141597526148</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0256293750135228</v>
+        <v>0.02667429199209437</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02337608399102464</v>
+        <v>0.02336066699353978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0311378330225125</v>
+        <v>0.0324591250391677</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02403916703769937</v>
+        <v>0.02420179196633399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02731741702882573</v>
+        <v>0.02740908297710121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01907350000692531</v>
+        <v>0.01938245899509639</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01859437499660999</v>
+        <v>0.01946454198332503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02810108300764114</v>
+        <v>0.0282521250192076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02173608302837238</v>
+        <v>0.02161941601661965</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02855883300071582</v>
+        <v>0.02813670795876533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236641600029543</v>
+        <v>0.02223591698566452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02293412503786385</v>
+        <v>0.02303629199741408</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01976812502834946</v>
+        <v>0.02024049998726696</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03035479201935232</v>
+        <v>0.03120904101524502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0204114579828456</v>
+        <v>0.02103908295975998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02515220904024318</v>
+        <v>0.02493258396862075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450070797931403</v>
+        <v>0.02483541698893532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0255254169460386</v>
+        <v>0.02523962501436472</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02770845801569521</v>
+        <v>0.02707400004146621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02750625001499429</v>
+        <v>0.02797137497691438</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02915633301017806</v>
+        <v>0.02918237500125542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02589404099853709</v>
+        <v>0.02553700003772974</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02167320903390646</v>
+        <v>0.02148837497225031</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01582629099721089</v>
+        <v>0.01547354203648865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02283291600178927</v>
+        <v>0.02207120804814622</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02753420895896852</v>
+        <v>0.02673079195665196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02724124997621402</v>
+        <v>0.02701395796611905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388029097346589</v>
+        <v>0.02469191700220108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02213649998884648</v>
+        <v>0.02218187501421198</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02237279195105657</v>
+        <v>0.02183879096992314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01910520798992366</v>
+        <v>0.01909750001505017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02402349998010322</v>
+        <v>0.02376495895441622</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02648991701425985</v>
+        <v>0.02640320803038776</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02135929197538644</v>
+        <v>0.02263783401576802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02345141698606312</v>
+        <v>0.02436512499116361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02076616702834144</v>
+        <v>0.02098179201129824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02195312501862645</v>
+        <v>0.021870750002563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02120004198513925</v>
+        <v>0.02068704197881743</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02117874997202307</v>
+        <v>0.02060716698179021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02778370800660923</v>
+        <v>0.02717295900220051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0270429159863852</v>
+        <v>0.02650020900182426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02630920801311731</v>
+        <v>0.0286722500459291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02006929204799235</v>
+        <v>0.0209785420447588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01962408301187679</v>
+        <v>0.019860458036419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03322237503016368</v>
+        <v>0.03305412497138605</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01951225002994761</v>
+        <v>0.02753050002502277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02326437504962087</v>
+        <v>0.02349500003037974</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401404199190438</v>
+        <v>0.0252636669902131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03197816701140255</v>
+        <v>0.03377487498801202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02380054199602455</v>
+        <v>0.02466404199367389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02222329203505069</v>
+        <v>0.02215175004675984</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01540899998508394</v>
+        <v>0.01516220800112933</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0229606669745408</v>
+        <v>0.02393808303168043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01889670803211629</v>
+        <v>0.01988237496698275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01805466698715463</v>
+        <v>0.01814537501195446</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02362833300139755</v>
+        <v>0.02450987498741597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02000358299119398</v>
+        <v>0.02278041699901223</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02437524998094887</v>
+        <v>0.02441070805070922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02170066704275087</v>
+        <v>0.02146495803026482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02969329198822379</v>
+        <v>0.02898483298486099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02111687499564141</v>
+        <v>0.02078558300854638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02015812497120351</v>
+        <v>0.02014824998332188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02922704198863357</v>
+        <v>0.02864604198839515</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02118987496942282</v>
+        <v>0.02085004199761897</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01843870803713799</v>
+        <v>0.01825800002552569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02337324997643009</v>
+        <v>0.0230089999968186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02205274999141693</v>
+        <v>0.02159104199381545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01922237500548363</v>
+        <v>0.01885304198367521</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01823654200416058</v>
+        <v>0.01796366600319743</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0267292499775067</v>
+        <v>0.02655908395536244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01888962497469038</v>
+        <v>0.01860999997006729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02955616603139788</v>
+        <v>0.0299744579824619</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450300002237782</v>
+        <v>0.02433020796161145</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02038200001697987</v>
+        <v>0.02008324995404109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02352541696745902</v>
+        <v>0.02307350002229214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02164454199373722</v>
+        <v>0.02132450003409758</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02374291600426659</v>
+        <v>0.02537799999117851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01920720800990239</v>
+        <v>0.01896549999946728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932241698727012</v>
+        <v>0.03047162498114631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0234328749938868</v>
+        <v>0.02345650002826005</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01929108297917992</v>
+        <v>0.01961287501035258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02459762501530349</v>
+        <v>0.02511395799228922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02484483399894089</v>
+        <v>0.02673641702858731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02343474997906014</v>
+        <v>0.0233332909992896</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02159870899049565</v>
+        <v>0.02179629198508337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01773062499705702</v>
+        <v>0.01770954194944352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02392329199938104</v>
+        <v>0.02479883300838992</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02176691597560421</v>
+        <v>0.02255512500414625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs9_GRID13/tour/UAVs9_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs9_GRID13/tour/UAVs9_GRID13_1920_16_Greedy_sequences.xlsx
@@ -622,7 +622,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02312658401206136</v>
+        <v>0.02226091700140387</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02687579102348536</v>
+        <v>0.02674612501868978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02058833400951698</v>
+        <v>0.01970799994887784</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02711787499720231</v>
+        <v>0.02676433400483802</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0281692499993369</v>
+        <v>0.02743324998300523</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02603091701166704</v>
+        <v>0.02622345898998901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02247491700109094</v>
+        <v>0.02198870800202712</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02017541701206937</v>
+        <v>0.02009458298562095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02267987502273172</v>
+        <v>0.02282133395783603</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02311916596954688</v>
+        <v>0.02225062501383945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023733296664432</v>
+        <v>0.02020608296152204</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02386141597526148</v>
+        <v>0.02390870900126174</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02667429199209437</v>
+        <v>0.02522233297349885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02336066699353978</v>
+        <v>0.02246350003406405</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0324591250391677</v>
+        <v>0.03037154203047976</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02420179196633399</v>
+        <v>0.0236456660204567</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02740908297710121</v>
+        <v>0.02721179195214063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01938245899509639</v>
+        <v>0.01848487497773021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01946454198332503</v>
+        <v>0.01824495801702142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0282521250192076</v>
+        <v>0.02748070802772418</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02161941601661965</v>
+        <v>0.02126737503567711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02813670795876533</v>
+        <v>0.02782874996773899</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02223591698566452</v>
+        <v>0.02171699999598786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02303629199741408</v>
+        <v>0.02288716699695215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02024049998726696</v>
+        <v>0.01934687496395782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03120904101524502</v>
+        <v>0.02975016599521041</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02103908295975998</v>
+        <v>0.02016287500737235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02493258396862075</v>
+        <v>0.02454704098636284</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02483541698893532</v>
+        <v>0.02412254200316966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02523962501436472</v>
+        <v>0.02527308400021866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02707400004146621</v>
+        <v>0.02687391696963459</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02797137497691438</v>
+        <v>0.02724612504243851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02918237500125542</v>
+        <v>0.02853541699005291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02553700003772974</v>
+        <v>0.02560770901618525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02148837497225031</v>
+        <v>0.0212336250115186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01547354203648865</v>
+        <v>0.01529212499735877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02207120804814622</v>
+        <v>0.02209541702177376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02673079195665196</v>
+        <v>0.02702391700586304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02701395796611905</v>
+        <v>0.0268837499897927</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02469191700220108</v>
+        <v>0.02345683297608048</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02218187501421198</v>
+        <v>0.02183749998221174</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02183879096992314</v>
+        <v>0.02187866601161659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01909750001505017</v>
+        <v>0.01862895803060383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02376495895441622</v>
+        <v>0.02342987502925098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02640320803038776</v>
+        <v>0.02611108403652906</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02263783401576802</v>
+        <v>0.02070641698082909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02436512499116361</v>
+        <v>0.02306012500775978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02098179201129824</v>
+        <v>0.02014962496468797</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.021870750002563</v>
+        <v>0.02149066596757621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02068704197881743</v>
+        <v>0.02054033300373703</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02060716698179021</v>
+        <v>0.02050033397972584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02717295900220051</v>
+        <v>0.02696504100458696</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02650020900182426</v>
+        <v>0.0265468749566935</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0286722500459291</v>
+        <v>0.02610066696070135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0209785420447588</v>
+        <v>0.01954887504689395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.019860458036419</v>
+        <v>0.0192672090488486</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03305412497138605</v>
+        <v>0.03299312497256324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02753050002502277</v>
+        <v>0.01910470897564664</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02349500003037974</v>
+        <v>0.02294741704827175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0252636669902131</v>
+        <v>0.02387708402238786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03377487498801202</v>
+        <v>0.03150687500601634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02466404199367389</v>
+        <v>0.02335908298846334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02215175004675984</v>
+        <v>0.02196158398874104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01516220800112933</v>
+        <v>0.01522699999623001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02393808303168043</v>
+        <v>0.0225861250073649</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01988237496698275</v>
+        <v>0.01836429198738188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01814537501195446</v>
+        <v>0.01776799996150658</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02450987498741597</v>
+        <v>0.02331945800688118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02278041699901223</v>
+        <v>0.019475249981042</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02441070805070922</v>
+        <v>0.02404841699171811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02146495803026482</v>
+        <v>0.02131124999141321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02898483298486099</v>
+        <v>0.02906241704476997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02078558300854638</v>
+        <v>0.02059924998320639</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02014824998332188</v>
+        <v>0.01946012501139194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02864604198839515</v>
+        <v>0.02871862496249378</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02085004199761897</v>
+        <v>0.02076662500621751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01825800002552569</v>
+        <v>0.01821158296661451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0230089999968186</v>
+        <v>0.02299437497276813</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02159104199381545</v>
+        <v>0.02190154202980921</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01885304198367521</v>
+        <v>0.01845137501368299</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01796366600319743</v>
+        <v>0.01792554202256724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02655908395536244</v>
+        <v>0.02636395901208743</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01860999997006729</v>
+        <v>0.01874624995980412</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0299744579824619</v>
+        <v>0.02938437496777624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02433020796161145</v>
+        <v>0.02386029099579901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02008324995404109</v>
+        <v>0.01977870799601078</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02307350002229214</v>
+        <v>0.02298433403484523</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02132450003409758</v>
+        <v>0.02121825003996491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02537799999117851</v>
+        <v>0.02296041598310694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01896549999946728</v>
+        <v>0.01880470803007483</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03047162498114631</v>
+        <v>0.02833708300022408</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02345650002826005</v>
+        <v>0.02262445795349777</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01961287501035258</v>
+        <v>0.01875716698123142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02511395799228922</v>
+        <v>0.02403804200002924</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02673641702858731</v>
+        <v>0.02476791699882597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0233332909992896</v>
+        <v>0.02274733403464779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02179629198508337</v>
+        <v>0.02132770797470585</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01770954194944352</v>
+        <v>0.01753654202912003</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02479883300838992</v>
+        <v>0.02312033297494054</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02255512500414625</v>
+        <v>0.02164512500166893</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
